--- a/嘉宾偏好_第二轮.xlsx
+++ b/嘉宾偏好_第二轮.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mumark/Desktop/Documents/AI Startup/Claude Code/Dating_Match/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mumark/Desktop/Documents/AI_Startup/Claude_Code/Dating_Match/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB795F29-8155-9449-BA06-4A29CC2EDA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F1CEA6-8C18-654A-BE9D-722A6323430E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15000" yWindow="4760" windowWidth="23460" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="偏好_两级排名_调整" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="44">
   <si>
     <t>嘉宾类型</t>
   </si>
@@ -521,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -550,7 +550,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -578,7 +578,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -681,30 +681,30 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -712,13 +712,13 @@
         <v>5</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -726,13 +726,13 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -740,13 +740,13 @@
         <v>5</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -754,13 +754,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -768,13 +768,13 @@
         <v>5</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -782,13 +782,13 @@
         <v>5</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -796,13 +796,13 @@
         <v>5</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -810,69 +810,13 @@
         <v>5</v>
       </c>
       <c r="B21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24">
-        <v>11</v>
-      </c>
-      <c r="C24" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
